--- a/moduli_aziende/birindellipaolo/moduli_compilati/REG-DOC-Registro_Documenti_SGQ.xlsx
+++ b/moduli_aziende/birindellipaolo/moduli_compilati/REG-DOC-Registro_Documenti_SGQ.xlsx
@@ -2,11 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASTER DOCUMENT REGISTER" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stati" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cronologia Revisioni" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,43 +29,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -70,12 +59,10 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -150,9 +137,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -190,7 +177,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -224,7 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -259,10 +245,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -440,79 +425,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="75.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="16.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="7" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="64.42578125" bestFit="1" customWidth="1" min="4" max="5"/>
-    <col width="84.5703125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="134.140625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="15.85546875" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="11" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="7" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="12.140625" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="5.42578125" bestFit="1" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Codice</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Titolo documento</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Sezione</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Norma</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Sottosezione</t>
+          <t>Processo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Rev.</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>RelPath</t>
+          <t>Data rev.</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Percorso</t>
+          <t>Stato</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Revisione_guess</t>
+          <t>Proprietario</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Data_guess</t>
+          <t>Distribuzione</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Pagine</t>
+          <t>Riesame</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -526,14 +493,50 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Manuale SGQ - Introduzione</t>
+          <t>Introduzione</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -548,9 +551,45 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -565,9 +604,45 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -582,9 +657,45 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -599,9 +710,45 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -616,9 +763,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -633,9 +816,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -650,9 +869,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -667,9 +922,45 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,9 +975,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -701,402 +1028,4193 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PFC-001</t>
+          <t>PROC-400</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Piano Fabbricazione e Controllo - Preparazione materiale</t>
+          <t>Monitoraggio del contesto</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Produzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PFC-002</t>
+          <t>PROC-530</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Piano Fabbricazione e Controllo - Carteggiatura</t>
+          <t>Organizzazione del personale</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Produzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PFC-003</t>
+          <t>PROC-610</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Piano Fabbricazione e Controllo - Preparazione vernici</t>
+          <t>Gestione rischi e opportunità</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Produzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PFC-004</t>
+          <t>PROC-620</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Piano Fabbricazione e Controllo - Applicazione fondo</t>
+          <t>Obiettivi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Produzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PFC-005</t>
+          <t>PROC-630</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Piano Fabbricazione e Controllo - Verniciatura manuale</t>
+          <t>Pianificazione modifiche</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Produzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PFC-006</t>
+          <t>PROC-710</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Piano Fabbricazione e Controllo - Verniciatura robotizzata</t>
+          <t>Gestione risorse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Produzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PFC-007</t>
+          <t>PROC-720</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Piano Fabbricazione e Controllo - Controllo finale</t>
+          <t>Persone e competenze</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Produzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PFC-008</t>
+          <t>PROC-740</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Piano Fabbricazione e Controllo - Imballaggio</t>
+          <t>Comunicazione</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Produzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IST-001</t>
+          <t>PROC-750</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Preparazione superfici</t>
+          <t>Informazioni documentate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Istruzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IST-002</t>
+          <t>PROC-820</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Preparazione miscela vernici</t>
+          <t>Requisiti del cliente</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Istruzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IST-003</t>
+          <t>PROC-830</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Utilizzo bilancia digitale</t>
+          <t>Progettazione</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Istruzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IST-004</t>
+          <t>PROC-840</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Utilizzo spessimetro</t>
+          <t>Outsourcing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Istruzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IST-005</t>
+          <t>PROC-850</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cambio colore impianto</t>
+          <t>Gestione del processo produttivo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Istruzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IST-006</t>
+          <t>PROC-870</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pulizia cabine</t>
+          <t>Prodotti non conformi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Istruzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IST-007</t>
+          <t>PROC-910</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gestione filtri cabine</t>
+          <t>Monitoraggio e misurazione</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Istruzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IST-008</t>
+          <t>PROC-920</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Utilizzo impianto robotizzato</t>
+          <t>Audit interni</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Istruzione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SCH-001</t>
+          <t>PROC-930</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Scheda Controllo Produzione</t>
+          <t>Riesame della Direzione</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Controllo</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>REG-001</t>
+          <t>PROC-1020</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Registro preparazione vernici</t>
+          <t>Azioni correttive e miglioramento</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Registrazione</t>
-        </is>
-      </c>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>REG-002</t>
+          <t>MOD-400-A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Registro controllo spessori</t>
+          <t>Modulo 400-A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Registrazione</t>
-        </is>
-      </c>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>REG-003</t>
+          <t>MOD-400-B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Registro manutenzione cabine</t>
+          <t>Modulo 400-B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Registrazione</t>
-        </is>
-      </c>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>REG-004</t>
+          <t>MOD-530-B</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Registro sostituzione filtri</t>
+          <t>Modulo 530-B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Registrazione</t>
-        </is>
-      </c>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>REG-005</t>
+          <t>MOD-530-C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Registro taratura strumenti</t>
+          <t>Modulo 530-C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Registrazione</t>
-        </is>
-      </c>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>MOD-610-B</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Modulo 610-B</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MOD-620-B</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Modulo 620-B</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MOD-710-A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Modulo 710-A</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MOD-710-B</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Modulo 710-B</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MOD-710-C</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Modulo 710-C</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MOD-710-D</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Modulo 710-D</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MOD-720-C</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Modulo 720-C</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MOD-720-F1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Modulo 720-F1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MOD-720-F2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Modulo 720-F2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MOD-720-G</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Modulo 720-G</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MOD-740-B</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Modulo 740-B</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MOD-840-A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Modulo 840-A</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MOD-850-B</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Modulo 850-B</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MOD-850-H</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Modulo 850-H</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MOD-850-I</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Modulo 850-I</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MOD-870-B</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Modulo 870-B</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MOD-910-C</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Modulo 910-C</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MOD-910-E</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Modulo 910-E</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MOD-910-G</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Modulo 910-G</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MOD-910-H</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Modulo 910-H</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MOD-920-A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Modulo 920-A</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MOD-920-B</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Modulo 920-B</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MOD-1020-A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Modulo 1020-A</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MOD-1020-B</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Modulo 1020-B</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>RSQ</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PFC-001</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Preparazione materiale</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PFC-002</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Carteggiatura</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PFC-003</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Preparazione vernici</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PFC-004</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Applicazione fondo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PFC-005</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Verniciatura manuale</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PFC-006</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Verniciatura robotizzata</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PFC-007</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Controllo finale</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PFC-008</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Imballaggio</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ITE-01</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Gestione del processo di Molding</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ITE</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ITE-02</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Procedura di resinatura involucro anteriore e posteriore</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ITE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>IST-001</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Preparazione superfici</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>IST-002</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Preparazione miscela vernici</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>IST-003</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Utilizzo bilancia digitale</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>IST-004</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Utilizzo spessimetro</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>IST-005</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Cambio colore impianto</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IST-006</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Pulizia cabine</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>IST-007</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Gestione filtri cabine</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IST-008</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Utilizzo impianto robotizzato</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SCH-001</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Scheda Controllo Produzione</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SCH</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>CQ</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>REG-001</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Preparazione vernici</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>REG-002</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Controllo spessori</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>REG-003</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Manutenzione cabine</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>REG-004</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Sostituzione filtri</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>REG-005</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Taratura strumenti</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>REG-006</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Registro pulizia cabine</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Registrazione</t>
-        </is>
-      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pulizia cabine</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STD-001</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Standard difetti verniciatura</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>CQ</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STD-002</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Standard accettabilità estetica</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>CQ</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STD-003</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Standard imballaggio</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>CQ</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Prefisso</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Descrizione</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Manuali</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PROC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Moduli</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Piani Fabbricazione e Controllo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ITE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Istruzioni Tecniche</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Istruzioni Operative</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SCH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Schede</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Registrazioni</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BOZZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OBSOLETO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rev.</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Descrizione modifica</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Autore</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/moduli_aziende/birindellipaolo/moduli_compilati/REG-DOC-Registro_Documenti_SGQ.xlsx
+++ b/moduli_aziende/birindellipaolo/moduli_compilati/REG-DOC-Registro_Documenti_SGQ.xlsx
@@ -134,6 +134,27 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterDocs" displayName="MasterDocs" ref="A1:L91" headerRowCount="1">
+  <autoFilter ref="A1:L91"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Codice"/>
+    <tableColumn id="2" name="Nome file"/>
+    <tableColumn id="3" name="Titolo documento"/>
+    <tableColumn id="4" name="Categoria"/>
+    <tableColumn id="5" name="Processo"/>
+    <tableColumn id="6" name="Rev."/>
+    <tableColumn id="7" name="Data rev."/>
+    <tableColumn id="8" name="Stato"/>
+    <tableColumn id="9" name="Proprietario"/>
+    <tableColumn id="10" name="Distribuzione"/>
+    <tableColumn id="11" name="Riesame"/>
+    <tableColumn id="12" name="Note"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -425,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,50 +457,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Nome file</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Titolo documento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Processo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Rev.</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Data rev.</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Proprietario</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Distribuzione</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Riesame</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -493,50 +519,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Introduzione</t>
+          <t>MAN-00_Introduzione.docx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Manuale - Introduzione</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -546,50 +577,55 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scopo e campo di applicazione</t>
+          <t>MAN-01_Scopo_e_campo_di_applicazione.docx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Manuale - Scopo e campo di applicazione</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -599,50 +635,55 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Riferimenti normativi</t>
+          <t>MAN-02_Riferimenti_normativi.docx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Manuale - Riferimenti normativi</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -652,50 +693,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Termini e definizioni</t>
+          <t>MAN-03_Termini_e_definizioni.docx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Manuale - Termini e definizioni</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -705,50 +751,55 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Contesto dell'organizzazione</t>
+          <t>MAN-04_Contesto_dell'organizzazione.docx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Manuale - Contesto dell'organizzazione</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -758,50 +809,55 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>MAN-05_Leadership.docx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Manuale - Leadership</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -811,50 +867,55 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pianificazione</t>
+          <t>MAN-06_Pianificazione.docx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Manuale - Pianificazione</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -864,50 +925,55 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supporto</t>
+          <t>MAN-07_Supporto.docx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Manuale - Supporto</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -917,50 +983,55 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Attività operative</t>
+          <t>MAN-08_Attività_operative.docx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Manuale - Attività operative</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -970,50 +1041,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Valutazione delle prestazioni</t>
+          <t>MAN-09_Valutazione_delle_prestazioni.docx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Manuale - Valutazione delle prestazioni</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1023,50 +1099,55 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Miglioramento</t>
+          <t>MAN-10_Miglioramento.docx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Manuale - Miglioramento</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1076,50 +1157,55 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Monitoraggio del contesto</t>
+          <t>PROC-400_Monitoraggio_del_contesto.docx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Procedura - Monitoraggio del contesto</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1129,50 +1215,55 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Organizzazione del personale</t>
+          <t>PROC-530_Organizzazione_del_personale.docx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Procedura - Organizzazione del personale</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1182,50 +1273,55 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gestione rischi e opportunità</t>
+          <t>PROC-610_Gestione_dei_rischi_e_delle_opportunità.docx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Procedura - Gestione dei rischi e delle opportunità</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1235,50 +1331,55 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Obiettivi</t>
+          <t>PROC-620_Obiettivi.docx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Procedura - Obiettivi</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1288,50 +1389,55 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pianificazione modifiche</t>
+          <t>PROC-630_Pianificazione_delle_modifiche.docx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Procedura - Pianificazione delle modifiche</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1341,50 +1447,55 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gestione risorse</t>
+          <t>PROC-710_Gestione_delle_risorse.docx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Procedura - Gestione delle risorse</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1394,50 +1505,55 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Persone e competenze</t>
+          <t>PROC-720_Persone_e_competenze.docx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Procedura - Persone e competenze</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1447,50 +1563,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Comunicazione</t>
+          <t>PROC-740_Comunicazione.docx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Procedura - Comunicazione</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1500,50 +1621,55 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Informazioni documentate</t>
+          <t>PROC-750_Informazioni_documentate.docx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Procedura - Informazioni documentate</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1553,50 +1679,55 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Requisiti del cliente</t>
+          <t>PROC-820_Requisiti_del_cliente.docx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Procedura - Requisiti del cliente</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1606,50 +1737,55 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Progettazione</t>
+          <t>PROC-830_Progettazione.docx</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Procedura - Progettazione</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1659,50 +1795,55 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Outsourcing</t>
+          <t>PROC-840_Outsourcing.docx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Procedura - Outsourcing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1712,3286 +1853,3889 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gestione del processo produttivo</t>
+          <t>PROC-850_Gestione_del_processo_produttivo.docx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Procedura - Gestione del processo produttivo</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PROC-870</t>
+          <t>PROC-854</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Prodotti non conformi</t>
+          <t>PROC-854_Preservazione.docx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Procedura - Preservazione</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PROC-910</t>
+          <t>PROC-870</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Monitoraggio e misurazione</t>
+          <t>PROC-870_Controllo_output_non_conformi.docx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>Procedura - Controllo output non conformi</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PROC-920</t>
+          <t>PROC-910</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Audit interni</t>
+          <t>PROC-910_Monitoraggio,_misurazione_e_analisi.docx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Procedura - Monitoraggio, misurazione e analisi</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PROC-930</t>
+          <t>PROC-920</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Riesame della Direzione</t>
+          <t>PROC-920_Audit_interni.docx</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Procedura - Audit interni</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PROC-1020</t>
+          <t>PROC-930</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Azioni correttive e miglioramento</t>
+          <t>PROC-930_Riesame_della_Direzione.docx</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>Procedura - Riesame della Direzione</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>PROC</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>05</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>VALIDATO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>Annuale</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MOD-400-A</t>
+          <t>PROC-1020</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Modulo 400-A</t>
+          <t>PROC-1020_Non_conformità_e_azioni_correttive.docx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MOD</t>
+          <t>Procedura - Non conformità e azioni correttive</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
+          <t>PROC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>Sistema Qualità</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>IMPLEMENTATO WIP</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>RSQ</t>
+          <t>VALIDATO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Quando necessario</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MOD-400-B</t>
+          <t>PROC-1030</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Modulo 400-B</t>
+          <t>PROC-1030_Miglioramento_continuo.docx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MOD</t>
+          <t>Procedura - Miglioramento continuo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sistema Qualità</t>
+          <t>PROC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>Sistema Qualità</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>IMPLEMENTATO WIP</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>RSQ</t>
+          <t>VALIDATO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Quando necessario</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Annuale</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MOD-530-B</t>
+          <t>MOD-400-A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Modulo 530-B</t>
+          <t>MOD-400-A_Contesto.xlsx</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Modulo - Contesto</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MOD-530-C</t>
+          <t>MOD-400-B</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Modulo 530-C</t>
+          <t>MOD-400-B_Parti_interessate.xlsx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Modulo - Parti interessate</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MOD-610-B</t>
+          <t>MOD-530-B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Modulo 610-B</t>
+          <t>MOD-530-B_Ruoli_e_requisiti.xlsx</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Modulo - Ruoli e requisiti</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MOD-620-B</t>
+          <t>MOD-530-C</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Modulo 620-B</t>
+          <t>MOD-530-C_Matrice_delle_responsabilità.xlsx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Modulo - Matrice delle responsabilità</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MOD-710-A</t>
+          <t>MOD-610-B</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Modulo 710-A</t>
+          <t>MOD-610-B_Risk_Management.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Modulo - Risk Management</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MOD-710-B</t>
+          <t>MOD-620-B</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Modulo 710-B</t>
+          <t>MOD-620-B_Pianificazione.xlsx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Modulo - Pianificazione</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MOD-710-C</t>
+          <t>MOD-710-A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Modulo 710-C</t>
+          <t>MOD-710-A_Ambienti_di_lavoro.xlsx</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Modulo - Ambienti di lavoro</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MOD-710-D</t>
+          <t>MOD-710-B</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Modulo 710-D</t>
+          <t>MOD-710-B_Dispositivi.xlsx</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>Modulo - Dispositivi</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MOD-720-C</t>
+          <t>MOD-710-C</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Modulo 720-C</t>
+          <t>MOD-710-C_Dispositivi.xlsx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>Modulo - Dispositivi</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MOD-720-F1</t>
+          <t>MOD-710-D</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Modulo 720-F1</t>
+          <t>MOD-710-D_Risorse_per_monitoraggio_e_misurazione.xlsx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>Modulo - Risorse per monitoraggio e misurazione</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MOD-720-F2</t>
+          <t>MOD-710-E</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Modulo 720-F2</t>
+          <t>MOD-710-E_Conoscenza_organizzativa.xlsx</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Modulo - Conoscenza organizzativa</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MOD-720-G</t>
+          <t>MOD-710-F</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Modulo 720-G</t>
+          <t>MOD-710-F_Supporti.xlsx</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>Modulo - Supporti</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MOD-740-B</t>
+          <t>MOD-720-C</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Modulo 740-B</t>
+          <t>MOD-720-C_Registro_formazione.xlsx</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Modulo - Registro formazione</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MOD-840-A</t>
+          <t>MOD-720-F.1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Modulo 840-A</t>
+          <t>MOD-720-F.1_Monitoraggio_formazione.xlsx</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Modulo - Monitoraggio formazione</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MOD-850-B</t>
+          <t>MOD-720-F.2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Modulo 850-B</t>
+          <t>MOD-720-F.2_Monitoraggio_formazione_CS.xlsx</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>Modulo - Monitoraggio formazione CS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MOD-850-H</t>
+          <t>MOD-720-G</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Modulo 850-H</t>
+          <t>MOD-720-G_Piano_formazione_annuale.xlsx</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Modulo - Piano formazione annuale</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MOD-850-I</t>
+          <t>MOD-740-A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Modulo 850-I</t>
+          <t>MOD-740-A_Comunicazioni.xlsx</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Modulo - Comunicazioni</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MOD-870-B</t>
+          <t>MOD-740-B</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Modulo 870-B</t>
+          <t>MOD-740-B_Monitoraggio_comunicazione.xlsx</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Modulo - Monitoraggio comunicazione</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MOD-910-C</t>
+          <t>MOD-840-A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Modulo 910-C</t>
+          <t>MOD-840-A_Elenco_fornitori_qualificati.xlsx</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>Modulo - Elenco fornitori qualificati</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MOD-910-E</t>
+          <t>MOD-850-B</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Modulo 910-E</t>
+          <t>MOD-850-B_Identificazione_e_tracciabilità.xlsx</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>Modulo - Identificazione e tracciabilità</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MOD-910-G</t>
+          <t>MOD-850-H</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Modulo 910-G</t>
+          <t>MOD-850-H_Controllo_per_variabili.xlsx</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Modulo - Controllo per variabili</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MOD-910-H</t>
+          <t>MOD-850-I</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Modulo 910-H</t>
+          <t>MOD-850-I_Controllo_NC_su_ordini.xlsx</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>Modulo - Controllo NC su ordini</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G54" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MOD-920-A</t>
+          <t>MOD-870-B</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Modulo 920-A</t>
+          <t>MOD-870-B_Prodotti_non_conformi.xlsx</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>Modulo - Prodotti non conformi</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MOD-920-B</t>
+          <t>MOD-910-C</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Modulo 920-B</t>
+          <t>MOD-910-C_Soddisfazione_clienti.xlsx</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>Modulo - Soddisfazione clienti</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MOD-1020-A</t>
+          <t>MOD-910-E</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Modulo 1020-A</t>
+          <t>MOD-910-E_Soddisfazione_persone.xlsx</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>Modulo - Soddisfazione persone</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MOD-1020-B</t>
+          <t>MOD-910-G</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Modulo 1020-B</t>
+          <t>MOD-910-G_Soddisfazione_fornitori.xlsx</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>Modulo - Soddisfazione fornitori</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>MOD</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Sistema Qualità</t>
-        </is>
-      </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>Sistema Qualità</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>RSQ</t>
-        </is>
-      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Master digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PFC-001</t>
+          <t>MOD-910-H</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Preparazione materiale</t>
+          <t>MOD-910-H_Performance.xlsx</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>Modulo - Performance</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Produzione</t>
+          <t>MOD</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>Sistema Qualità</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Produzione</t>
-        </is>
-      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PFC-002</t>
+          <t>MOD-920-A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Carteggiatura</t>
+          <t>MOD-920-A_Programma_audit.xlsx</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>Modulo - Programma audit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Produzione</t>
+          <t>MOD</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>Sistema Qualità</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Produzione</t>
-        </is>
-      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PFC-003</t>
+          <t>MOD-920-B</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Preparazione vernici</t>
+          <t>MOD-920-B_Rapporto_audit.xlsx</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>Modulo - Rapporto audit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Produzione</t>
+          <t>MOD</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>Sistema Qualità</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Produzione</t>
-        </is>
-      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PFC-004</t>
+          <t>MOD-1020-A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Applicazione fondo</t>
+          <t>MOD-1020-A_Non_conformità.xlsx</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>Modulo - Non conformità</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Produzione</t>
+          <t>MOD</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>Sistema Qualità</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Produzione</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PFC-005</t>
+          <t>MOD-1020-B</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Verniciatura manuale</t>
+          <t>MOD-1020-B_Azioni_correttive.xlsx</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>Modulo - Azioni correttive</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Produzione</t>
+          <t>MOD</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>Sistema Qualità</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Produzione</t>
-        </is>
-      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Digitale</t>
+          <t>RSQ</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PFC-006</t>
+          <t>ITE-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Verniciatura robotizzata</t>
+          <t>ITE-01_Gestione_del_processo_di_Molding.docx</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>Istruzione Tecnica - Gestione del processo di Molding</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>ITE</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>IMPLEMENTATO WIP</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Digitale</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PFC-007</t>
+          <t>ITE-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Controllo finale</t>
+          <t>ITE-02_Procedura_di_resinatura_involucro_anteriore_e_posteriore.docx</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>Istruzione Tecnica - Procedura di resinatura involucro anteriore e posteriore</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>ITE</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>IMPLEMENTATO WIP</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
+          <t>VALIDATO</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Digitale</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>Master digitale</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PFC-008</t>
+          <t>PFC-001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Imballaggio</t>
+          <t>PFC-001_Preparazione_materiale.xlsx</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>Piano di Fabbricazione e Controllo - Preparazione materiale</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>PFC</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G66" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ITE-01</t>
+          <t>PFC-002</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Gestione del processo di Molding</t>
+          <t>PFC-002_Carteggiatura.xlsx</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ITE</t>
+          <t>Piano di Fabbricazione e Controllo - Carteggiatura</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>VALIDATO</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Master digitale</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ITE-02</t>
+          <t>PFC-003</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Procedura di resinatura involucro anteriore e posteriore</t>
+          <t>PFC-003_Preparazione_vernici.xlsx</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ITE</t>
+          <t>Piano di Fabbricazione e Controllo - Preparazione vernici</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>00</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>VALIDATO</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Master digitale</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IST-001</t>
+          <t>PFC-004</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Preparazione superfici</t>
+          <t>PFC-004_Applicazione_fondo.xlsx</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>Piano di Fabbricazione e Controllo - Applicazione fondo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IST-002</t>
+          <t>PFC-005</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Preparazione miscela vernici</t>
+          <t>PFC-005_Verniciatura_manuale.xlsx</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>Piano di Fabbricazione e Controllo - Verniciatura manuale</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IST-003</t>
+          <t>PFC-006</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Utilizzo bilancia digitale</t>
+          <t>PFC-006_Verniciatura_robotizzata.xlsx</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>Piano di Fabbricazione e Controllo - Verniciatura robotizzata</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IST-004</t>
+          <t>PFC-007</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Utilizzo spessimetro</t>
+          <t>PFC-007_Controllo_finale.xlsx</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>Piano di Fabbricazione e Controllo - Controllo finale</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IST-005</t>
+          <t>PFC-008</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cambio colore impianto</t>
+          <t>PFC-008_Imballaggio.xlsx</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>Piano di Fabbricazione e Controllo - Imballaggio</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IST-006</t>
+          <t>IST-001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pulizia cabine</t>
+          <t>IST-001_Preparazione_superfici.docx</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
+          <t>Istruzione Operativa - Preparazione superfici</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
           <t>IST</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IST-007</t>
+          <t>IST-002</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gestione filtri cabine</t>
+          <t>IST-002_Preparazione_miscela_vernici.docx</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>Istruzione Operativa - Preparazione miscela vernici</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
           <t>IST</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IST-008</t>
+          <t>IST-003</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Utilizzo impianto robotizzato</t>
+          <t>IST-003_Utilizzo_bilancia_digitale.docx</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>Istruzione Operativa - Utilizzo bilancia digitale</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
           <t>IST</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SCH-001</t>
+          <t>IST-004</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Scheda Controllo Produzione</t>
+          <t>IST-004_Utilizzo_spessimetro.docx</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SCH</t>
+          <t>Istruzione Operativa - Utilizzo spessimetro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>CQ</t>
-        </is>
-      </c>
       <c r="I77" t="inlineStr">
         <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>REG-001</t>
+          <t>IST-005</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Preparazione vernici</t>
+          <t>IST-005_Cambio_colore_impianto.docx</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>Istruzione Operativa - Cambio colore impianto</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>REG-002</t>
+          <t>IST-006</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Controllo spessori</t>
+          <t>IST-006_Pulizia_cabine.docx</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>Istruzione Operativa - Pulizia cabine</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>REG-003</t>
+          <t>IST-007</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Manutenzione cabine</t>
+          <t>IST-007_Gestione_filtri_cabine.docx</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>Istruzione Operativa - Gestione filtri cabine</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>REG-004</t>
+          <t>IST-008</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sostituzione filtri</t>
+          <t>IST-008_Utilizzo_impianto_robotizzato.docx</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>Istruzione Operativa - Utilizzo impianto robotizzato</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G81" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>REG-005</t>
+          <t>SCH-001</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Taratura strumenti</t>
+          <t>SCH-001_Scheda_Controllo_Produzione.xlsx</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>Scheda - Controllo Produzione</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>SCH</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Produzione</t>
-        </is>
-      </c>
       <c r="I82" t="inlineStr">
         <is>
+          <t>CQ</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>REG-006</t>
+          <t>REG-001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pulizia cabine</t>
+          <t>REG-001_Preparazione_vernici.xlsx</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>Registro - Preparazione vernici</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>REG</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STD-001</t>
+          <t>REG-002</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Standard difetti verniciatura</t>
+          <t>REG-002_Controllo_spessori.xlsx</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>STD</t>
+          <t>Registro - Controllo spessori</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>CQ</t>
-        </is>
-      </c>
       <c r="I84" t="inlineStr">
         <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STD-002</t>
+          <t>REG-003</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Standard accettabilità estetica</t>
+          <t>REG-003_Manutenzione_cabine.xlsx</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>STD</t>
+          <t>Registro - Manutenzione cabine</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
       <c r="G85" t="inlineStr">
         <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>CQ</t>
-        </is>
-      </c>
       <c r="I85" t="inlineStr">
         <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>REG-004</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>REG-004_Sostituzione_filtri.xlsx</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Registro - Sostituzione filtri</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>REG-005</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>REG-005_Taratura_strumenti.xlsx</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Registro - Taratura strumenti</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>REG-006</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>REG-006_Pulizia_cabine.xlsx</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Registro - Pulizia cabine</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>REG</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STD-001</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>STD-001_Difetti_di_verniciatura.pdf</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Standard - Difetti di verniciatura</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>CQ</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STD-002</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>STD-002_Accettabilità_estetica.pdf</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Standard - Accettabilità estetica</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Produzione</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>IMPLEMENTATO WIP</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>CQ</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Digitale</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Quando necessario</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>STD-003</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Standard imballaggio</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>STD-003_Imballaggio.pdf</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Standard - Imballaggio</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>STD</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Produzione</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t>IMPLEMENTATO WIP</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>CQ</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>Digitale</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>Quando necessario</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -5060,7 +5804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Piani Fabbricazione e Controllo</t>
+          <t>PFC</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5949,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Descrizione modifica</t>
+          <t>Descrizione</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
